--- a/tiflow-chargeitem/fhir-error-codes/1.0.0-draft/CodeSystem-tiflow-chargeitem-operation-outcome-details-cs.xlsx
+++ b/tiflow-chargeitem/fhir-error-codes/1.0.0-draft/CodeSystem-tiflow-chargeitem-operation-outcome-details-cs.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-30T06:44:55+00:00</t>
+    <t>2026-04-02T12:36:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/tiflow-chargeitem/fhir-error-codes/1.0.0-draft/CodeSystem-tiflow-chargeitem-operation-outcome-details-cs.xlsx
+++ b/tiflow-chargeitem/fhir-error-codes/1.0.0-draft/CodeSystem-tiflow-chargeitem-operation-outcome-details-cs.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-02T12:36:25+00:00</t>
+    <t>2026-04-10T08:10:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/tiflow-chargeitem/fhir-error-codes/1.0.0-draft/CodeSystem-tiflow-chargeitem-operation-outcome-details-cs.xlsx
+++ b/tiflow-chargeitem/fhir-error-codes/1.0.0-draft/CodeSystem-tiflow-chargeitem-operation-outcome-details-cs.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-10T08:10:54+00:00</t>
+    <t>2026-04-13T14:31:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/tiflow-chargeitem/fhir-error-codes/1.0.0-draft/CodeSystem-tiflow-chargeitem-operation-outcome-details-cs.xlsx
+++ b/tiflow-chargeitem/fhir-error-codes/1.0.0-draft/CodeSystem-tiflow-chargeitem-operation-outcome-details-cs.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-13T14:31:53+00:00</t>
+    <t>2026-04-14T04:55:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
